--- a/data/Plantilla_LBEn_M3_modelo.xlsx
+++ b/data/Plantilla_LBEn_M3_modelo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\gdrive_luisflorez\Mi unidad\PROYECTOS_LF\ProyectosE2\LBEn_EDIF_app\pruebasResol\M3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\gdrive_luisflorez\Mi unidad\PROYECTOS_LF\ProyectosE2\LBEn_EDIF_app\LBEn_APP_Resol016\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8E91E5-80A7-469A-A161-AD9260C8FC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C77B95-34F9-483E-82F5-5848BF0D1B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18510" yWindow="-150" windowWidth="17990" windowHeight="8910" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="150">
   <si>
     <t>SISTEMA DE GESTIÓN LBEn — M3 — Modelos Estadísticos</t>
   </si>
@@ -484,6 +484,12 @@
   <si>
     <t>Desviación Real-Calculado
 (kWh) — app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p &gt; 0.05 → Homocedasticidad ✓: Los errores son constantes (Modelo estable y confiable).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p ≤ 0.05 → Heterocedasticidad ✗: Los errores varían (El modelo pierde precisión en ciertos rangos de consumo).</t>
   </si>
 </sst>
 </file>
@@ -1064,32 +1070,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1711,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:F36"/>
+  <dimension ref="B1:F38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2037,8 +2043,26 @@
         <v>83</v>
       </c>
     </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B37" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B38" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B4:E4"/>
@@ -2076,7 +2100,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="61" t="s">
         <v>145</v>
       </c>
       <c r="C1" s="35"/>
@@ -2086,7 +2110,7 @@
       <c r="G1" s="35"/>
     </row>
     <row r="2" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="62" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="35"/>
@@ -2096,27 +2120,27 @@
       <c r="G2" s="35"/>
     </row>
     <row r="4" spans="2:13" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>85</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="33"/>
       <c r="E4" s="9"/>
-      <c r="I4" s="60" t="s">
+      <c r="I4" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
     </row>
     <row r="5" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="56" t="s">
         <v>87</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="18"/>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="55" t="s">
         <v>88</v>
       </c>
       <c r="J5" s="33"/>
@@ -2129,12 +2153,12 @@
       <c r="M5" s="19"/>
     </row>
     <row r="6" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="55" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="18"/>
-      <c r="I6" s="54" t="s">
+      <c r="I6" s="55" t="s">
         <v>92</v>
       </c>
       <c r="J6" s="33"/>
@@ -2145,12 +2169,12 @@
       <c r="M6" s="19"/>
     </row>
     <row r="7" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="18"/>
-      <c r="I7" s="54" t="s">
+      <c r="I7" s="55" t="s">
         <v>95</v>
       </c>
       <c r="J7" s="33"/>
@@ -2161,12 +2185,12 @@
       <c r="M7" s="19"/>
     </row>
     <row r="8" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="55" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="18"/>
-      <c r="I8" s="54" t="s">
+      <c r="I8" s="55" t="s">
         <v>98</v>
       </c>
       <c r="J8" s="33"/>
@@ -2177,12 +2201,12 @@
       <c r="M8" s="19"/>
     </row>
     <row r="9" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="55" t="s">
         <v>100</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="18"/>
-      <c r="I9" s="54" t="s">
+      <c r="I9" s="55" t="s">
         <v>101</v>
       </c>
       <c r="J9" s="33"/>
@@ -2193,12 +2217,12 @@
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="2:13" s="9" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="55" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="33"/>
       <c r="D10" s="18"/>
-      <c r="I10" s="54" t="s">
+      <c r="I10" s="55" t="s">
         <v>104</v>
       </c>
       <c r="J10" s="33"/>
@@ -2209,28 +2233,28 @@
       <c r="M10" s="19"/>
     </row>
     <row r="11" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="55" t="s">
         <v>106</v>
       </c>
       <c r="C11" s="33"/>
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="55" t="s">
         <v>107</v>
       </c>
       <c r="C12" s="33"/>
       <c r="D12" s="18"/>
     </row>
     <row r="13" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="33"/>
       <c r="D13" s="18"/>
     </row>
     <row r="14" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="55" t="s">
         <v>109</v>
       </c>
       <c r="C14" s="33"/>
@@ -2238,28 +2262,28 @@
     </row>
     <row r="15" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="57" t="s">
         <v>110</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="33"/>
     </row>
     <row r="17" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="55" t="s">
         <v>111</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="19"/>
     </row>
     <row r="18" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="55" t="s">
         <v>112</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="19"/>
     </row>
     <row r="19" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="55" t="s">
         <v>113</v>
       </c>
       <c r="C19" s="33"/>
@@ -2270,7 +2294,7 @@
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="55" t="s">
         <v>114</v>
       </c>
       <c r="C20" s="33"/>
@@ -2280,7 +2304,7 @@
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="55" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="33"/>
@@ -2290,7 +2314,7 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="55" t="s">
         <v>116</v>
       </c>
       <c r="C22" s="33"/>
@@ -2300,7 +2324,7 @@
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="55" t="s">
         <v>117</v>
       </c>
       <c r="C23" s="33"/>
@@ -2321,7 +2345,7 @@
     </row>
     <row r="26" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="59" t="s">
         <v>118</v>
       </c>
       <c r="C27" s="35"/>
@@ -2329,7 +2353,7 @@
       <c r="E27" s="35"/>
     </row>
     <row r="28" spans="2:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="58" t="s">
         <v>119</v>
       </c>
       <c r="C28" s="35"/>
@@ -2337,7 +2361,7 @@
       <c r="E28" s="35"/>
     </row>
     <row r="29" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="60" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="33"/>
@@ -2495,6 +2519,58 @@
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B69:C69"/>
     <mergeCell ref="B92:C92"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="B68:C68"/>
@@ -2511,58 +2587,6 @@
     <mergeCell ref="B85:C85"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B63:C63"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B82:C82"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2673,32 +2697,32 @@
       <c r="B5" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
-      <c r="V5" s="61"/>
-      <c r="W5" s="61"/>
-      <c r="X5" s="61"/>
-      <c r="Y5" s="61"/>
-      <c r="Z5" s="61"/>
-      <c r="AA5" s="61"/>
-      <c r="AB5" s="61"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="54"/>
     </row>
     <row r="6" spans="2:28" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="13" t="s">

--- a/data/Plantilla_LBEn_M3_modelo.xlsx
+++ b/data/Plantilla_LBEn_M3_modelo.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\gdrive_luisflorez\Mi unidad\PROYECTOS_LF\ProyectosE2\LBEn_EDIF_app\LBEn_APP_Resol016\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luisa Hernandez\Downloads\LBEn_APP_Resol016\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C77B95-34F9-483E-82F5-5848BF0D1B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456D37C4-D21E-4A48-A952-EFFA9A97D346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Período_Base" sheetId="2" r:id="rId2"/>
-    <sheet name="Diag_Modelo" sheetId="3" r:id="rId3"/>
-    <sheet name="Modelo_LBEn" sheetId="4" r:id="rId4"/>
-    <sheet name="Monitoreo" sheetId="5" r:id="rId5"/>
+    <sheet name="Monitoreo" sheetId="5" r:id="rId3"/>
+    <sheet name="Diag_Modelo" sheetId="3" r:id="rId4"/>
+    <sheet name="Modelo_LBEn" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
@@ -496,7 +496,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1041,6 +1041,9 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1061,41 +1064,38 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1366,7 +1366,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1375,28 +1375,28 @@
     <col min="5" max="5" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:4" ht="31.5" customHeight="1">
       <c r="B1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
     </row>
-    <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:4" ht="18" customHeight="1">
       <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
     </row>
-    <row r="4" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" ht="19.5" customHeight="1">
       <c r="B4" s="36" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
     </row>
-    <row r="5" spans="2:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4" ht="25" customHeight="1">
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4" ht="36" customHeight="1">
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4" ht="37.5" customHeight="1">
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4" ht="25" customHeight="1">
       <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
@@ -1440,14 +1440,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:4" ht="19.5" customHeight="1">
       <c r="B11" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
     </row>
-    <row r="12" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:4" ht="18" customHeight="1">
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="D12" s="33"/>
     </row>
-    <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:4" ht="18" customHeight="1">
       <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="D13" s="33"/>
     </row>
-    <row r="14" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:4" ht="18" customHeight="1">
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D14" s="33"/>
     </row>
-    <row r="15" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:4" ht="18" customHeight="1">
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
@@ -1502,7 +1502,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AG7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -1525,7 +1525,7 @@
     <col min="26" max="26" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:33" ht="27.75" customHeight="1">
       <c r="B1" s="40" t="s">
         <v>24</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="S1" s="40"/>
       <c r="AG1" s="11"/>
     </row>
-    <row r="2" spans="2:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:33" ht="15.75" customHeight="1">
       <c r="B2" s="41" t="s">
         <v>25</v>
       </c>
@@ -1571,10 +1571,10 @@
       <c r="S2" s="41"/>
       <c r="AG2" s="12"/>
     </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:33">
       <c r="AG3" s="12"/>
     </row>
-    <row r="4" spans="2:33" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:33" ht="44.5" customHeight="1">
       <c r="B4" s="38" t="s">
         <v>26</v>
       </c>
@@ -1597,10 +1597,10 @@
       <c r="S4" s="39"/>
       <c r="AG4" s="12"/>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:33">
       <c r="W5" s="12"/>
     </row>
-    <row r="6" spans="2:33" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:33" ht="43.5" customHeight="1">
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="W6" s="12"/>
     </row>
-    <row r="7" spans="2:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:33" ht="15.75" customHeight="1">
       <c r="B7" s="10" t="s">
         <v>43</v>
       </c>
@@ -1716,887 +1716,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:F38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:6" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-    </row>
-    <row r="3" spans="2:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="46"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-    </row>
-    <row r="5" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-    </row>
-    <row r="6" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="23" x14ac:dyDescent="0.35">
-      <c r="B7" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="23" x14ac:dyDescent="0.35">
-      <c r="B9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="23" x14ac:dyDescent="0.35">
-      <c r="B10" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-    </row>
-    <row r="14" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-    </row>
-    <row r="17" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-    </row>
-    <row r="19" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-    </row>
-    <row r="20" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-    </row>
-    <row r="22" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-    </row>
-    <row r="23" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-    </row>
-    <row r="25" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B31" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-    </row>
-    <row r="32" spans="2:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-    </row>
-    <row r="33" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="34" spans="2:5" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B36" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B37" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B38" s="50" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B31:E31"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:M92"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="3" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="26.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="61" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-    </row>
-    <row r="2" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-    </row>
-    <row r="4" spans="2:13" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="9"/>
-      <c r="I4" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-    </row>
-    <row r="5" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="18"/>
-      <c r="I5" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="M5" s="19"/>
-    </row>
-    <row r="6" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="18"/>
-      <c r="I6" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="18"/>
-      <c r="I7" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="19"/>
-    </row>
-    <row r="8" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="18"/>
-      <c r="I8" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8" s="19"/>
-    </row>
-    <row r="9" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="55" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="18"/>
-      <c r="I9" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="J9" s="33"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="2:13" s="9" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="18"/>
-      <c r="I10" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="J10" s="33"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="M10" s="19"/>
-    </row>
-    <row r="11" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="18"/>
-    </row>
-    <row r="15" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="57" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="33"/>
-    </row>
-    <row r="17" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="19"/>
-    </row>
-    <row r="18" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="55" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="19"/>
-    </row>
-    <row r="19" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="19"/>
-      <c r="F19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="19"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="19"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="19"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="2:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="19"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="2:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B27" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-    </row>
-    <row r="28" spans="2:11" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-    </row>
-    <row r="29" spans="2:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B30" s="52"/>
-      <c r="C30" s="35"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B31" s="52"/>
-      <c r="C31" s="35"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B32" s="52"/>
-      <c r="C32" s="35"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B33" s="52"/>
-      <c r="C33" s="35"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B34" s="52"/>
-      <c r="C34" s="35"/>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B61" s="52"/>
-      <c r="C61" s="35"/>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B62" s="52"/>
-      <c r="C62" s="35"/>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B63" s="52"/>
-      <c r="C63" s="35"/>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B64" s="52"/>
-      <c r="C64" s="35"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B65" s="52"/>
-      <c r="C65" s="35"/>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B66" s="52"/>
-      <c r="C66" s="35"/>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B67" s="52"/>
-      <c r="C67" s="35"/>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B68" s="52"/>
-      <c r="C68" s="35"/>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="52"/>
-      <c r="C69" s="35"/>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B70" s="52"/>
-      <c r="C70" s="35"/>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B71" s="52"/>
-      <c r="C71" s="35"/>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B72" s="52"/>
-      <c r="C72" s="35"/>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B73" s="52"/>
-      <c r="C73" s="35"/>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B74" s="52"/>
-      <c r="C74" s="35"/>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B75" s="52"/>
-      <c r="C75" s="35"/>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B76" s="52"/>
-      <c r="C76" s="35"/>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B77" s="52"/>
-      <c r="C77" s="35"/>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B78" s="52"/>
-      <c r="C78" s="35"/>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B79" s="52"/>
-      <c r="C79" s="35"/>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B80" s="52"/>
-      <c r="C80" s="35"/>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B81" s="52"/>
-      <c r="C81" s="35"/>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B82" s="52"/>
-      <c r="C82" s="35"/>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B83" s="52"/>
-      <c r="C83" s="35"/>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B84" s="52"/>
-      <c r="C84" s="35"/>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B85" s="52"/>
-      <c r="C85" s="35"/>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B86" s="52"/>
-      <c r="C86" s="35"/>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B87" s="52"/>
-      <c r="C87" s="35"/>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B88" s="52"/>
-      <c r="C88" s="35"/>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B89" s="52"/>
-      <c r="C89" s="35"/>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B90" s="52"/>
-      <c r="C90" s="35"/>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B91" s="52"/>
-      <c r="C91" s="35"/>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B92" s="52"/>
-      <c r="C92" s="35"/>
-    </row>
-  </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B63:C63"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AB7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2631,7 +1753,7 @@
     <col min="38" max="38" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:28" ht="27.75" customHeight="1">
       <c r="B1" s="40" t="s">
         <v>121</v>
       </c>
@@ -2662,7 +1784,7 @@
       <c r="AA1" s="35"/>
       <c r="AB1" s="35"/>
     </row>
-    <row r="2" spans="2:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:28" ht="15.75" customHeight="1">
       <c r="B2" s="41" t="s">
         <v>122</v>
       </c>
@@ -2693,38 +1815,38 @@
       <c r="AA2" s="35"/>
       <c r="AB2" s="35"/>
     </row>
-    <row r="5" spans="2:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:28" ht="19.5" customHeight="1">
       <c r="B5" s="63" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="54"/>
-      <c r="X5" s="54"/>
-      <c r="Y5" s="54"/>
-      <c r="Z5" s="54"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="54"/>
-    </row>
-    <row r="6" spans="2:28" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="61"/>
+      <c r="V5" s="61"/>
+      <c r="W5" s="61"/>
+      <c r="X5" s="61"/>
+      <c r="Y5" s="61"/>
+      <c r="Z5" s="61"/>
+      <c r="AA5" s="61"/>
+      <c r="AB5" s="61"/>
+    </row>
+    <row r="6" spans="2:28" ht="56.5" customHeight="1">
       <c r="B6" s="13" t="s">
         <v>27</v>
       </c>
@@ -2807,7 +1929,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="7" spans="2:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:28" ht="15.75" customHeight="1">
       <c r="B7" s="10" t="s">
         <v>43</v>
       </c>
@@ -2889,4 +2011,882 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B1:F38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="29.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="6" customHeight="1"/>
+    <row r="2" spans="2:6" ht="30" customHeight="1">
+      <c r="B2" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+    </row>
+    <row r="3" spans="2:6" ht="14" customHeight="1">
+      <c r="B3" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="47"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+    </row>
+    <row r="5" spans="2:6" ht="20" customHeight="1">
+      <c r="B5" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+    </row>
+    <row r="6" spans="2:6" ht="20" customHeight="1">
+      <c r="B6" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="23">
+      <c r="B7" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="23">
+      <c r="B9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="23">
+      <c r="B10" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="20" customHeight="1">
+      <c r="B13" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+    </row>
+    <row r="14" spans="2:6" ht="20" customHeight="1">
+      <c r="B14" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="20" customHeight="1">
+      <c r="B15" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="2:6" ht="20" customHeight="1">
+      <c r="B16" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" spans="2:6" ht="20" customHeight="1">
+      <c r="B17" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="2:6" ht="20" customHeight="1">
+      <c r="B18" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+    </row>
+    <row r="19" spans="2:6" ht="20" customHeight="1">
+      <c r="B19" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="2:6" ht="20" customHeight="1">
+      <c r="B20" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+    </row>
+    <row r="22" spans="2:6" ht="20" customHeight="1">
+      <c r="B22" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+    </row>
+    <row r="23" spans="2:6" ht="20" customHeight="1"/>
+    <row r="24" spans="2:6" ht="20" customHeight="1">
+      <c r="B24" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+    </row>
+    <row r="25" spans="2:6" ht="20" customHeight="1">
+      <c r="B25" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+    </row>
+    <row r="32" spans="2:6" ht="20" customHeight="1">
+      <c r="B32" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+    </row>
+    <row r="33" spans="2:5" ht="20" customHeight="1"/>
+    <row r="34" spans="2:5" ht="20" customHeight="1">
+      <c r="B34" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="25"/>
+      <c r="E36" s="27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B31:E31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:M92"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="3" customWidth="1"/>
+    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="26.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="27.75" customHeight="1">
+      <c r="B1" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+    </row>
+    <row r="2" spans="2:13" ht="18" customHeight="1">
+      <c r="B2" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+    </row>
+    <row r="4" spans="2:13" ht="35" customHeight="1">
+      <c r="B4" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="9"/>
+      <c r="I4" s="60" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+    </row>
+    <row r="5" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B5" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="18"/>
+      <c r="I5" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="33"/>
+      <c r="K5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B6" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="18"/>
+      <c r="I6" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="33"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B7" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="18"/>
+      <c r="I7" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="19"/>
+    </row>
+    <row r="8" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B8" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="18"/>
+      <c r="I8" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="33"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="19"/>
+    </row>
+    <row r="9" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B9" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="18"/>
+      <c r="I9" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="19"/>
+    </row>
+    <row r="10" spans="2:13" s="9" customFormat="1" ht="34" customHeight="1">
+      <c r="B10" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="18"/>
+      <c r="I10" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B11" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B12" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="33"/>
+      <c r="D12" s="18"/>
+    </row>
+    <row r="13" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B13" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B14" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="33"/>
+      <c r="D14" s="18"/>
+    </row>
+    <row r="15" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1"/>
+    <row r="16" spans="2:13" s="9" customFormat="1" ht="24.5" customHeight="1">
+      <c r="B16" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="33"/>
+    </row>
+    <row r="17" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1">
+      <c r="B17" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="2:11" s="9" customFormat="1" ht="25" customHeight="1">
+      <c r="B18" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="2:11" ht="25" customHeight="1">
+      <c r="B19" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="19"/>
+      <c r="F19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="2:11" ht="25" customHeight="1">
+      <c r="B20" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="19"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="2:11" ht="25" customHeight="1">
+      <c r="B21" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="33"/>
+      <c r="D21" s="19"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="2:11" ht="25" customHeight="1">
+      <c r="B22" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="19"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="2:11" ht="25" customHeight="1">
+      <c r="B23" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="33"/>
+      <c r="D23" s="19"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="2:11" ht="19.5" customHeight="1">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="2:11" ht="27.75" customHeight="1">
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="2:11" ht="26" customHeight="1"/>
+    <row r="27" spans="2:11">
+      <c r="B27" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+    </row>
+    <row r="28" spans="2:11" ht="31" customHeight="1">
+      <c r="B28" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+    </row>
+    <row r="29" spans="2:11" ht="26" customHeight="1">
+      <c r="B29" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="52"/>
+      <c r="C30" s="35"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="52"/>
+      <c r="C31" s="35"/>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="52"/>
+      <c r="C32" s="35"/>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="52"/>
+      <c r="C33" s="35"/>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="52"/>
+      <c r="C34" s="35"/>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" s="52"/>
+      <c r="C61" s="35"/>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" s="52"/>
+      <c r="C62" s="35"/>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" s="52"/>
+      <c r="C63" s="35"/>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" s="52"/>
+      <c r="C64" s="35"/>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" s="52"/>
+      <c r="C65" s="35"/>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" s="52"/>
+      <c r="C66" s="35"/>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" s="52"/>
+      <c r="C67" s="35"/>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" s="52"/>
+      <c r="C68" s="35"/>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" s="52"/>
+      <c r="C69" s="35"/>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" s="52"/>
+      <c r="C70" s="35"/>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71" s="52"/>
+      <c r="C71" s="35"/>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="B72" s="52"/>
+      <c r="C72" s="35"/>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73" s="52"/>
+      <c r="C73" s="35"/>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="B74" s="52"/>
+      <c r="C74" s="35"/>
+    </row>
+    <row r="75" spans="2:3">
+      <c r="B75" s="52"/>
+      <c r="C75" s="35"/>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76" s="52"/>
+      <c r="C76" s="35"/>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" s="52"/>
+      <c r="C77" s="35"/>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78" s="52"/>
+      <c r="C78" s="35"/>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79" s="52"/>
+      <c r="C79" s="35"/>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="B80" s="52"/>
+      <c r="C80" s="35"/>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81" s="52"/>
+      <c r="C81" s="35"/>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82" s="52"/>
+      <c r="C82" s="35"/>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" s="52"/>
+      <c r="C83" s="35"/>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="B84" s="52"/>
+      <c r="C84" s="35"/>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85" s="52"/>
+      <c r="C85" s="35"/>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="B86" s="52"/>
+      <c r="C86" s="35"/>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="B87" s="52"/>
+      <c r="C87" s="35"/>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88" s="52"/>
+      <c r="C88" s="35"/>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89" s="52"/>
+      <c r="C89" s="35"/>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90" s="52"/>
+      <c r="C90" s="35"/>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" s="52"/>
+      <c r="C91" s="35"/>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="B92" s="52"/>
+      <c r="C92" s="35"/>
+    </row>
+  </sheetData>
+  <mergeCells count="68">
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B82:C82"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>